--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="368">
   <si>
     <t>Code</t>
   </si>
@@ -1114,6 +1114,18 @@
   </si>
   <si>
     <t>AMARU GTC</t>
+  </si>
+  <si>
+    <t>JKY01</t>
+  </si>
+  <si>
+    <t>2017 NISSAN GT-R (R35)</t>
+  </si>
+  <si>
+    <t>JKY27</t>
+  </si>
+  <si>
+    <t>CUSTOM/PERSONNALISÉ '70 HONDA N600</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1207,6 +1219,9 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4711,10 +4726,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="43.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -4889,6 +4905,76 @@
         <v>11</v>
       </c>
       <c r="K5" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="25">
+        <v>46113</v>
+      </c>
+      <c r="G6" s="24">
+        <v>299</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="26">
+        <v>399</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="25">
+        <v>46143</v>
+      </c>
+      <c r="G7" s="24">
+        <v>299</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="26">
+        <v>399</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="18" t="s">
         <v>10</v>
       </c>
     </row>

--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>
     <sheet name="Hot Wheels Premium" sheetId="2" r:id="rId2"/>
-    <sheet name="Hot Wheels Treaure Hunt" sheetId="3" r:id="rId3"/>
+    <sheet name="Hot Wheels Treasure Hunt" sheetId="3" r:id="rId3"/>
     <sheet name="Hot Wheels 5 Packs" sheetId="4" r:id="rId4"/>
     <sheet name="Matchbox Card" sheetId="5" r:id="rId5"/>
     <sheet name="Matchbox Box" sheetId="6" r:id="rId6"/>

--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>
@@ -4797,7 +4797,7 @@
         <v>699</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="K2" s="18" t="s">
         <v>10</v>
@@ -7383,7 +7383,7 @@
         <v>609</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>10</v>
@@ -8068,7 +8068,7 @@
         <v>1617</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>10</v>

--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="366">
   <si>
     <t>Code</t>
   </si>
@@ -364,12 +364,6 @@
   </si>
   <si>
     <t>Jeep® Wrangler Superlift</t>
-  </si>
-  <si>
-    <t>JHP74</t>
-  </si>
-  <si>
-    <t>2002 Mazda RX-7 Spirit R</t>
   </si>
   <si>
     <t>SOLD</t>
@@ -1575,19 +1569,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F2" s="6">
         <v>46023</v>
@@ -1610,19 +1604,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F3" s="6">
         <v>46023</v>
@@ -1645,19 +1639,19 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F4" s="12">
         <v>46235</v>
@@ -1680,19 +1674,19 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F5" s="12">
         <v>46082</v>
@@ -1715,19 +1709,19 @@
     </row>
     <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F6" s="4">
         <v>46023</v>
@@ -1750,19 +1744,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F7" s="4">
         <v>46054</v>
@@ -1785,19 +1779,19 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F8" s="4">
         <v>46023</v>
@@ -1820,19 +1814,19 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F9" s="4">
         <v>46023</v>
@@ -1855,19 +1849,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F10" s="4">
         <v>46054</v>
@@ -1890,19 +1884,19 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F11" s="12">
         <v>46082</v>
@@ -1925,19 +1919,19 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F12" s="4">
         <v>46023</v>
@@ -1960,19 +1954,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F13" s="4">
         <v>46023</v>
@@ -1995,19 +1989,19 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F14" s="12">
         <v>46204</v>
@@ -2030,19 +2024,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F15" s="12">
         <v>46082</v>
@@ -2065,19 +2059,19 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F16" s="12">
         <v>46082</v>
@@ -2100,19 +2094,19 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F17" s="12">
         <v>46082</v>
@@ -2135,19 +2129,19 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F18" s="12">
         <v>46082</v>
@@ -2170,19 +2164,19 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F19" s="4">
         <v>45839</v>
@@ -2205,19 +2199,19 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F20" s="4">
         <v>46023</v>
@@ -2240,19 +2234,19 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F21" s="4">
         <v>46023</v>
@@ -2275,19 +2269,19 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F22" s="4">
         <v>46054</v>
@@ -2310,19 +2304,19 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F23" s="12">
         <v>46082</v>
@@ -2345,19 +2339,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F24" s="12">
         <v>46082</v>
@@ -2380,19 +2374,19 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F25" s="12">
         <v>46082</v>
@@ -2415,19 +2409,19 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F26" s="12">
         <v>46082</v>
@@ -2450,19 +2444,19 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F27" s="12">
         <v>46082</v>
@@ -2485,19 +2479,19 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F28" s="12">
         <v>46113</v>
@@ -2520,19 +2514,19 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F29" s="12">
         <v>46143</v>
@@ -2555,19 +2549,19 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F30" s="12">
         <v>46174</v>
@@ -2590,19 +2584,19 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F31" s="12">
         <v>46204</v>
@@ -2625,19 +2619,19 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F32" s="4">
         <v>46023</v>
@@ -2660,19 +2654,19 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F33" s="4">
         <v>46023</v>
@@ -2695,19 +2689,19 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F34" s="4">
         <v>46023</v>
@@ -2730,19 +2724,19 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F35" s="4">
         <v>46023</v>
@@ -2765,19 +2759,19 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F36" s="4">
         <v>45962</v>
@@ -2800,19 +2794,19 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F37" s="4">
         <v>46023</v>
@@ -2835,19 +2829,19 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F38" s="4">
         <v>46023</v>
@@ -2870,19 +2864,19 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F39" s="4">
         <v>46023</v>
@@ -2905,19 +2899,19 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F40" s="4">
         <v>46054</v>
@@ -2940,19 +2934,19 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F41" s="4">
         <v>45992</v>
@@ -2975,19 +2969,19 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F42" s="4">
         <v>46023</v>
@@ -3010,19 +3004,19 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F43" s="4">
         <v>46023</v>
@@ -3045,19 +3039,19 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F44" s="4">
         <v>46023</v>
@@ -3080,19 +3074,19 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F45" s="4">
         <v>46023</v>
@@ -3115,19 +3109,19 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F46" s="4">
         <v>46054</v>
@@ -3150,19 +3144,19 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F47" s="6">
         <v>46023</v>
@@ -3185,19 +3179,19 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F48" s="6">
         <v>46023</v>
@@ -3220,19 +3214,19 @@
     </row>
     <row r="49" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E49" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F49" s="4">
         <v>46023</v>
@@ -3255,19 +3249,19 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F50" s="4">
         <v>46023</v>
@@ -4770,19 +4764,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F2" s="17">
         <v>46023</v>
@@ -4797,7 +4791,7 @@
         <v>699</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K2" s="18" t="s">
         <v>10</v>
@@ -4805,19 +4799,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F3" s="20">
         <v>46174</v>
@@ -4840,19 +4834,19 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>193</v>
       </c>
       <c r="F4" s="17">
         <v>45839</v>
@@ -4875,19 +4869,19 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F5" s="17">
         <v>46054</v>
@@ -4910,19 +4904,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F6" s="25">
         <v>46113</v>
@@ -4945,19 +4939,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F7" s="25">
         <v>46143</v>
@@ -5028,19 +5022,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F2" s="17">
         <v>45658</v>
@@ -5063,19 +5057,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F3" s="17">
         <v>45658</v>
@@ -5098,19 +5092,19 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F4" s="17">
         <v>46023</v>
@@ -5133,19 +5127,19 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F5" s="17">
         <v>45839</v>
@@ -5168,19 +5162,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F6" s="17">
         <v>46054</v>
@@ -5203,19 +5197,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F7" s="17">
         <v>45839</v>
@@ -5238,19 +5232,19 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F8" s="17">
         <v>45839</v>
@@ -5273,19 +5267,19 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F9" s="17">
         <v>45870</v>
@@ -5357,19 +5351,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F2" s="21">
         <v>45413</v>
@@ -5452,7 +5446,7 @@
         <v>57</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F2" s="23">
         <v>2026</v>
@@ -5487,7 +5481,7 @@
         <v>59</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F3" s="23">
         <v>2026</v>
@@ -5522,7 +5516,7 @@
         <v>61</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F4" s="23">
         <v>2026</v>
@@ -5557,7 +5551,7 @@
         <v>61</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F5" s="23">
         <v>2026</v>
@@ -5592,7 +5586,7 @@
         <v>63</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F6" s="23">
         <v>2026</v>
@@ -5627,7 +5621,7 @@
         <v>59</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F7" s="23">
         <v>2026</v>
@@ -5650,7 +5644,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>9</v>
@@ -5659,10 +5653,10 @@
         <v>12</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F8" s="23">
         <v>2026</v>
@@ -5697,7 +5691,7 @@
         <v>65</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F9" s="23">
         <v>2026</v>
@@ -5732,7 +5726,7 @@
         <v>67</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F10" s="23">
         <v>2026</v>
@@ -5767,7 +5761,7 @@
         <v>69</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F11" s="23">
         <v>2026</v>
@@ -5802,7 +5796,7 @@
         <v>71</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F12" s="23">
         <v>2026</v>
@@ -5825,7 +5819,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>9</v>
@@ -5834,10 +5828,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F13" s="23">
         <v>2026</v>
@@ -5872,7 +5866,7 @@
         <v>73</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F14" s="23">
         <v>2026</v>
@@ -5907,7 +5901,7 @@
         <v>75</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F15" s="23">
         <v>2026</v>
@@ -5942,7 +5936,7 @@
         <v>77</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F16" s="23">
         <v>2026</v>
@@ -5977,7 +5971,7 @@
         <v>79</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F17" s="23">
         <v>2026</v>
@@ -6012,7 +6006,7 @@
         <v>81</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F18" s="23">
         <v>2026</v>
@@ -6047,7 +6041,7 @@
         <v>83</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F19" s="23">
         <v>2026</v>
@@ -6082,7 +6076,7 @@
         <v>85</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F20" s="23">
         <v>2026</v>
@@ -6117,7 +6111,7 @@
         <v>87</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F21" s="23">
         <v>2026</v>
@@ -6152,7 +6146,7 @@
         <v>89</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F22" s="23">
         <v>2026</v>
@@ -6187,7 +6181,7 @@
         <v>91</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F23" s="23">
         <v>2026</v>
@@ -6222,7 +6216,7 @@
         <v>93</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F24" s="23">
         <v>2026</v>
@@ -6257,7 +6251,7 @@
         <v>95</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F25" s="23">
         <v>2026</v>
@@ -6292,7 +6286,7 @@
         <v>97</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F26" s="23">
         <v>2026</v>
@@ -6327,7 +6321,7 @@
         <v>99</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F27" s="23">
         <v>2026</v>
@@ -6350,7 +6344,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>9</v>
@@ -6359,10 +6353,10 @@
         <v>12</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F28" s="23">
         <v>2026</v>
@@ -6385,7 +6379,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>9</v>
@@ -6394,10 +6388,10 @@
         <v>12</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F29" s="23">
         <v>2026</v>
@@ -6420,7 +6414,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>9</v>
@@ -6429,10 +6423,10 @@
         <v>12</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F30" s="23">
         <v>2026</v>
@@ -6455,7 +6449,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>9</v>
@@ -6464,10 +6458,10 @@
         <v>12</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F31" s="23">
         <v>2026</v>
@@ -6495,7 +6489,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="32.77734375" customWidth="1"/>
@@ -6550,7 +6544,7 @@
         <v>101</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F2" s="2">
         <v>2026</v>
@@ -6585,7 +6579,7 @@
         <v>103</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F3" s="2">
         <v>2026</v>
@@ -6620,7 +6614,7 @@
         <v>105</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F4" s="2">
         <v>2026</v>
@@ -6655,7 +6649,7 @@
         <v>107</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F5" s="2">
         <v>2026</v>
@@ -6690,7 +6684,7 @@
         <v>107</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F6" s="2">
         <v>2025</v>
@@ -6725,7 +6719,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F7" s="2">
         <v>2025</v>
@@ -6760,7 +6754,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F8" s="2">
         <v>2026</v>
@@ -6795,7 +6789,7 @@
         <v>105</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F9" s="2">
         <v>2026</v>
@@ -6830,7 +6824,7 @@
         <v>113</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F10" s="2">
         <v>2026</v>
@@ -6865,7 +6859,7 @@
         <v>103</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F11" s="2">
         <v>2026</v>
@@ -6888,7 +6882,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -6897,10 +6891,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F12" s="2">
         <v>2026</v>
@@ -6912,18 +6906,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>9</v>
@@ -6932,10 +6926,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2">
         <v>2026</v>
@@ -6947,7 +6941,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="2">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>11</v>
@@ -6958,7 +6952,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>9</v>
@@ -6967,10 +6961,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F14" s="2">
         <v>2026</v>
@@ -6982,7 +6976,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>11</v>
@@ -6993,7 +6987,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
@@ -7002,10 +6996,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F15" s="2">
         <v>2026</v>
@@ -7017,7 +7011,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="2">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>11</v>
@@ -7028,7 +7022,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
@@ -7040,7 +7034,7 @@
         <v>119</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F16" s="2">
         <v>2026</v>
@@ -7052,7 +7046,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="2">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>11</v>
@@ -7063,7 +7057,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>9</v>
@@ -7072,10 +7066,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F17" s="2">
         <v>2026</v>
@@ -7087,7 +7081,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>11</v>
@@ -7098,7 +7092,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -7107,10 +7101,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F18" s="2">
         <v>2026</v>
@@ -7122,7 +7116,7 @@
         <v>12</v>
       </c>
       <c r="I18" s="2">
-        <v>289</v>
+        <v>219</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>11</v>
@@ -7133,7 +7127,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -7142,10 +7136,10 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F19" s="2">
         <v>2026</v>
@@ -7157,7 +7151,7 @@
         <v>12</v>
       </c>
       <c r="I19" s="2">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>11</v>
@@ -7180,7 +7174,7 @@
         <v>124</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F20" s="2">
         <v>2026</v>
@@ -7203,7 +7197,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>9</v>
@@ -7212,10 +7206,10 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F21" s="2">
         <v>2026</v>
@@ -7238,7 +7232,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -7247,10 +7241,10 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F22" s="2">
         <v>2026</v>
@@ -7268,41 +7262,6 @@
         <v>11</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F23" s="2">
-        <v>2026</v>
-      </c>
-      <c r="G23" s="2">
-        <v>179</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="2">
-        <v>269</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7383,7 +7342,7 @@
         <v>609</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>10</v>
@@ -7896,16 +7855,16 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>13</v>
@@ -7932,16 +7891,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>13</v>
@@ -7968,16 +7927,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>13</v>
@@ -8004,16 +7963,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>13</v>
@@ -8068,7 +8027,7 @@
         <v>1617</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>10</v>
@@ -8184,16 +8143,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>13</v>
@@ -8220,16 +8179,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>13</v>
@@ -8256,16 +8215,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>13</v>
@@ -8292,16 +8251,16 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>13</v>
@@ -8328,16 +8287,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>13</v>
@@ -8364,16 +8323,16 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>13</v>
@@ -8400,16 +8359,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>13</v>
@@ -8436,16 +8395,16 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>13</v>
@@ -8472,16 +8431,16 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>13</v>
@@ -8508,16 +8467,16 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>13</v>
@@ -8544,16 +8503,16 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>13</v>
@@ -8580,16 +8539,16 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>13</v>
@@ -8616,16 +8575,16 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>13</v>
@@ -8652,16 +8611,16 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>13</v>
@@ -8688,16 +8647,16 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>13</v>
@@ -8724,16 +8683,16 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>13</v>
@@ -8760,16 +8719,16 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>13</v>
@@ -8796,16 +8755,16 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>13</v>
@@ -8832,16 +8791,16 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>13</v>
@@ -8868,16 +8827,16 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>13</v>
@@ -8904,16 +8863,16 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>13</v>
@@ -8940,16 +8899,16 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>13</v>
@@ -8976,16 +8935,16 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>13</v>
@@ -9012,16 +8971,16 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>13</v>
@@ -9048,16 +9007,16 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>13</v>
@@ -9084,16 +9043,16 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>13</v>
@@ -9120,16 +9079,16 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>13</v>
@@ -9156,16 +9115,16 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>13</v>
@@ -9192,16 +9151,16 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>13</v>
@@ -9228,16 +9187,16 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>13</v>
@@ -9264,16 +9223,16 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>13</v>

--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>

--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>
@@ -1631,7 +1631,7 @@
         <v>269</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>10</v>
@@ -1841,7 +1841,7 @@
         <v>289</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>10</v>
@@ -7883,7 +7883,7 @@
         <v>986</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>10</v>

--- a/inventory/Inventory.xlsx
+++ b/inventory/Inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Hot Wheels Mainline" sheetId="1" r:id="rId1"/>
@@ -7084,7 +7084,7 @@
         <v>289</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>10</v>
@@ -8927,7 +8927,7 @@
         <v>887</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>10</v>
